--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260218_203005.xlsx
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
